--- a/healthcare_forms/023_coronavirus_awareness_survey--healthcare_forms.xlsx
+++ b/healthcare_forms/023_coronavirus_awareness_survey--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>congestion_or_stuffy_nose</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sore throat</t>
+          <t>Congestion or stuffy nose</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>congestion_or_stuffy_nose</t>
+          <t>coughing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Congestion or stuffy nose</t>
+          <t>Coughing</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>coughing</t>
+          <t>sneezing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Coughing</t>
+          <t>Sneezing</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sneezing</t>
+          <t>loss_of_taste_or_smell</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sneezing</t>
+          <t>Loss of taste or smell</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>loss_of_taste_or_smell</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Loss of taste or smell</t>
+          <t>Loss of appetite</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>loss_of_smell</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loss of appetite</t>
+          <t>Loss of smell</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>muscle_aches_or_pains</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Loss of smell</t>
+          <t>Muscle aches or pains</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>muscle_aches_or_pains</t>
+          <t>abnormal_heart_rate_or_rhythm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Muscle aches or pains</t>
+          <t>Abnormal heart rate or rhythm</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Chest pain</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>abnormal_heart_rate_or_rhythm</t>
+          <t>loss_of_taste</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Abnormal heart rate or rhythm</t>
+          <t>Loss of taste</t>
         </is>
       </c>
     </row>
@@ -1363,80 +1363,80 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chest pain</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>symptoms_page_choices</t>
+          <t>contact_tracing_confirmation_page_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Loss of taste</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>symptoms_page_choices</t>
+          <t>contact_tracing_confirmation_page_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>contact_tracing_confirmation_page_choices</t>
+          <t>healthcare_worker_info_page_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>contact_tracing_confirmation_page_choices</t>
+          <t>healthcare_worker_info_page_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>healthcare_assistant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Healthcare assistant</t>
         </is>
       </c>
     </row>
@@ -1465,78 +1465,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nurse</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>healthcare_worker_info_page_choices</t>
+          <t>healthcare_worker_info_confirmation_page_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>healthcare_assistant</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Healthcare assistant</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>healthcare_worker_info_page_choices</t>
+          <t>healthcare_worker_info_confirmation_page_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>healthcare_worker_info_confirmation_page_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>healthcare_worker_info_confirmation_page_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>False</t>
         </is>
